--- a/StructureDefinition-primary-track.xlsx
+++ b/StructureDefinition-primary-track.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/primary-track</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/primary-track</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-25T13:18:28+00:00</t>
+    <t>2026-10-29T07:06:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -344,7 +344,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/ValueSet/tracks</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/ValueSet/tracks</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -692,7 +692,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.94921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-primary-track.xlsx
+++ b/StructureDefinition-primary-track.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:06:30+00:00</t>
+    <t>2026-10-29T08:26:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-primary-track.xlsx
+++ b/StructureDefinition-primary-track.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:26:45+00:00</t>
+    <t>2026-10-29T09:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-primary-track.xlsx
+++ b/StructureDefinition-primary-track.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:23:29+00:00</t>
+    <t>2026-10-29T13:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-primary-track.xlsx
+++ b/StructureDefinition-primary-track.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:05:39+00:00</t>
+    <t>2026-10-29T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-primary-track.xlsx
+++ b/StructureDefinition-primary-track.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T15:50:41+00:00</t>
+    <t>2026-10-29T16:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-primary-track.xlsx
+++ b/StructureDefinition-primary-track.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T16:44:10+00:00</t>
+    <t>2026-10-30T09:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
